--- a/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
+++ b/modeleLogiqueCorps/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4424" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4444" uniqueCount="398">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T12:22:25+00:00</t>
+    <t>2026-06-30T08:22:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -485,6 +485,9 @@
 </t>
   </si>
   <si>
+    <t>Can serve as a target of a linkHtml reference</t>
+  </si>
+  <si>
     <t>Section.classCode</t>
   </si>
   <si>
@@ -674,6 +677,9 @@
     <t>Titre de la section</t>
   </si>
   <si>
+    <t>If valued, it is to be rendered as part of the narrative content of the clinical document body.</t>
+  </si>
+  <si>
     <t>Section.text</t>
   </si>
   <si>
@@ -684,10 +690,25 @@
     <t>Bloc narratif</t>
   </si>
   <si>
+    <t>Also referred to as the CDA Narrative Block</t>
+  </si>
+  <si>
     <t>Section.confidentialityCode</t>
   </si>
   <si>
+    <t>Controls the disclosure of information in this section</t>
+  </si>
+  <si>
+    <t>A value for Section.confidentialityCode overrides the value propagated from StructuredBody.</t>
+  </si>
+  <si>
     <t>Section.languageCode</t>
+  </si>
+  <si>
+    <t>Human language of character data</t>
+  </si>
+  <si>
+    <t>A value for Section.languageCode overrides the value propagated from StructuredBody.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/all-languages</t>
@@ -700,6 +721,15 @@
 </t>
   </si>
   <si>
+    <t>Primary target of the entries recorded in a section</t>
+  </si>
+  <si>
+    <t>Most of the time the subject is the same as the recordTarget, but need not be, for instance when the subject is a fetus observed in an obstetrical ultrasound.</t>
+  </si>
+  <si>
+    <t>The subject participant can be ascribed to a CDA section or a CDA entry. It propagates to nested components, unless overridden. The subject of a document is presumed to be the patient.</t>
+  </si>
+  <si>
     <t>Section.author</t>
   </si>
   <si>
@@ -707,6 +737,9 @@
 </t>
   </si>
   <si>
+    <t>The author participant can be ascribed to a CDA section, where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.informant</t>
   </si>
   <si>
@@ -714,6 +747,9 @@
 </t>
   </si>
   <si>
+    <t>The informant participant can be ascribed to a CDA section where it overrides the value(s) propagated from the CDA header.</t>
+  </si>
+  <si>
     <t>Section.entry</t>
   </si>
   <si>
@@ -1017,6 +1053,12 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/InfrastructureRoot
 </t>
+  </si>
+  <si>
+    <t>Used to nest a Section within a Section</t>
+  </si>
+  <si>
+    <t>Context propagates to nested sections</t>
   </si>
   <si>
     <t>Section.component.nullFlavor</t>
@@ -1540,7 +1582,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="148.87109375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -3961,7 +4003,9 @@
       <c r="K24" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="L24" s="2"/>
+      <c r="L24" t="s" s="2">
+        <v>152</v>
+      </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4032,10 +4076,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4069,7 +4113,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>74</v>
@@ -4091,7 +4135,7 @@
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>74</v>
@@ -4109,7 +4153,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4129,10 +4173,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4166,7 +4210,7 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>74</v>
@@ -4188,7 +4232,7 @@
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>74</v>
@@ -4206,7 +4250,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4226,10 +4270,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4243,7 +4287,7 @@
         <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>74</v>
@@ -4255,10 +4299,10 @@
         <v>95</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4309,7 +4353,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -4329,10 +4373,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4346,7 +4390,7 @@
         <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>74</v>
@@ -4355,13 +4399,13 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4412,7 +4456,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4432,10 +4476,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4533,10 +4577,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4565,7 +4609,7 @@
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4577,7 +4621,7 @@
         <v>74</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>74</v>
@@ -4616,7 +4660,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4636,17 +4680,17 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>75</v>
@@ -4668,7 +4712,7 @@
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4680,7 +4724,7 @@
         <v>74</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>74</v>
@@ -4719,7 +4763,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4739,17 +4783,17 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4771,7 +4815,7 @@
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4783,7 +4827,7 @@
         <v>74</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>74</v>
@@ -4822,7 +4866,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4842,17 +4886,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>80</v>
@@ -4874,7 +4918,7 @@
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4925,7 +4969,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4945,17 +4989,17 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>75</v>
@@ -4977,7 +5021,7 @@
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4989,7 +5033,7 @@
         <v>74</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>74</v>
@@ -5028,7 +5072,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5048,10 +5092,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5074,11 +5118,11 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5129,7 +5173,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -5149,10 +5193,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5179,7 +5223,7 @@
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5230,7 +5274,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5250,17 +5294,17 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
@@ -5278,11 +5322,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5333,7 +5377,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5353,17 +5397,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>80</v>
@@ -5381,11 +5425,11 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5436,7 +5480,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5456,17 +5500,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>80</v>
@@ -5484,11 +5528,11 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5539,7 +5583,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -5559,10 +5603,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5576,7 +5620,7 @@
         <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>74</v>
@@ -5585,16 +5629,18 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>74</v>
       </c>
@@ -5642,7 +5688,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5662,10 +5708,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5679,7 +5725,7 @@
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>
@@ -5688,15 +5734,17 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>74</v>
@@ -5745,7 +5793,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5765,10 +5813,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5791,12 +5839,16 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="L42" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
-      <c r="O42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>74</v>
       </c>
@@ -5844,7 +5896,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5864,10 +5916,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5892,10 +5944,14 @@
       <c r="K43" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="L43" s="2"/>
+      <c r="L43" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="O43" t="s" s="2">
+        <v>224</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>74</v>
       </c>
@@ -5923,7 +5979,7 @@
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>74</v>
@@ -5941,7 +5997,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5961,10 +6017,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -5987,12 +6043,18 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="L44" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="M44" s="2"/>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="N44" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>230</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>74</v>
       </c>
@@ -6040,7 +6102,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6060,10 +6122,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6086,12 +6148,14 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>74</v>
       </c>
@@ -6139,7 +6203,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6159,10 +6223,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6185,12 +6249,14 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+      <c r="O46" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>74</v>
       </c>
@@ -6238,7 +6304,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6258,10 +6324,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6275,7 +6341,7 @@
         <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>
@@ -6284,7 +6350,7 @@
         <v>74</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
@@ -6325,7 +6391,7 @@
         <v>74</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="AC47" s="2"/>
       <c r="AD47" t="s" s="2">
@@ -6335,7 +6401,7 @@
         <v>124</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -6355,13 +6421,13 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>74</v>
@@ -6383,7 +6449,7 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
@@ -6436,7 +6502,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -6456,10 +6522,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6557,10 +6623,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6658,10 +6724,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6759,10 +6825,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6860,10 +6926,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -6963,10 +7029,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7066,10 +7132,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7169,10 +7235,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7272,10 +7338,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7373,10 +7439,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7406,7 +7472,7 @@
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
@@ -7432,7 +7498,7 @@
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>74</v>
@@ -7450,7 +7516,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7470,10 +7536,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7507,7 +7573,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>74</v>
@@ -7549,7 +7615,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -7569,10 +7635,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7595,7 +7661,7 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7648,7 +7714,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -7668,10 +7734,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7694,7 +7760,7 @@
         <v>74</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -7747,7 +7813,7 @@
         <v>74</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -7767,10 +7833,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7793,7 +7859,7 @@
         <v>74</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -7846,7 +7912,7 @@
         <v>74</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -7866,10 +7932,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7892,7 +7958,7 @@
         <v>74</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -7945,7 +8011,7 @@
         <v>74</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -7965,10 +8031,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -7991,7 +8057,7 @@
         <v>74</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
@@ -8044,7 +8110,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -8064,10 +8130,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8090,10 +8156,10 @@
         <v>74</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
@@ -8145,7 +8211,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8165,10 +8231,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8191,7 +8257,7 @@
         <v>74</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
@@ -8244,7 +8310,7 @@
         <v>74</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8264,10 +8330,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8290,7 +8356,7 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8343,7 +8409,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8363,10 +8429,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8389,7 +8455,7 @@
         <v>74</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
@@ -8442,7 +8508,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8462,13 +8528,13 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>74</v>
@@ -8490,7 +8556,7 @@
         <v>74</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
@@ -8543,7 +8609,7 @@
         <v>74</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8563,10 +8629,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8664,10 +8730,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8765,10 +8831,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -8866,10 +8932,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -8967,10 +9033,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9070,10 +9136,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9173,10 +9239,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9276,10 +9342,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9379,10 +9445,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9480,10 +9546,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9513,7 +9579,7 @@
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
@@ -9539,7 +9605,7 @@
       </c>
       <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>74</v>
@@ -9557,7 +9623,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9577,10 +9643,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9614,7 +9680,7 @@
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>74</v>
@@ -9656,7 +9722,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9676,10 +9742,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -9702,7 +9768,7 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -9755,7 +9821,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9775,10 +9841,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -9801,7 +9867,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -9854,7 +9920,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9874,10 +9940,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9900,7 +9966,7 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -9953,7 +10019,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -9973,10 +10039,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>270</v>
+        <v>282</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9999,7 +10065,7 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
@@ -10052,7 +10118,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -10072,10 +10138,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10098,7 +10164,7 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
@@ -10151,7 +10217,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10171,10 +10237,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -10197,7 +10263,7 @@
         <v>74</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
@@ -10250,7 +10316,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10270,10 +10336,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -10296,7 +10362,7 @@
         <v>74</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
@@ -10349,7 +10415,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10369,10 +10435,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -10395,10 +10461,10 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="M88" s="2"/>
       <c r="N88" s="2"/>
@@ -10450,7 +10516,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10470,10 +10536,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10496,7 +10562,7 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
@@ -10549,7 +10615,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10569,10 +10635,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10583,10 +10649,10 @@
         <v>75</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>74</v>
@@ -10595,12 +10661,16 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="L90" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
+      <c r="O90" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>74</v>
       </c>
@@ -10636,7 +10706,7 @@
         <v>74</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="AC90" s="2"/>
       <c r="AD90" t="s" s="2">
@@ -10646,7 +10716,7 @@
         <v>124</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10666,10 +10736,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10767,10 +10837,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10868,10 +10938,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10969,10 +11039,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11070,10 +11140,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11173,10 +11243,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11276,10 +11346,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -11379,10 +11449,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -11482,10 +11552,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -11583,10 +11653,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -11613,7 +11683,7 @@
       </c>
       <c r="L100" s="2"/>
       <c r="M100" t="s" s="2">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -11622,7 +11692,7 @@
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>74</v>
@@ -11664,7 +11734,7 @@
         <v>74</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -11684,10 +11754,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -11721,7 +11791,7 @@
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>74</v>
@@ -11763,7 +11833,7 @@
         <v>74</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -11783,10 +11853,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -11809,7 +11879,7 @@
         <v>74</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>335</v>
+        <v>349</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -11862,7 +11932,7 @@
         <v>74</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>75</v>
@@ -11882,13 +11952,13 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>336</v>
+        <v>350</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>337</v>
+        <v>351</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>74</v>
@@ -11910,12 +11980,16 @@
         <v>74</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="L103" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="M103" s="2"/>
       <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
+      <c r="O103" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>74</v>
       </c>
@@ -11963,7 +12037,7 @@
         <v>74</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -11983,10 +12057,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12084,10 +12158,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>339</v>
+        <v>353</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12185,10 +12259,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>340</v>
+        <v>354</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12286,10 +12360,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -12387,10 +12461,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -12490,10 +12564,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>343</v>
+        <v>357</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -12593,10 +12667,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>344</v>
+        <v>358</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -12696,10 +12770,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -12799,10 +12873,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>346</v>
+        <v>360</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -12900,10 +12974,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>347</v>
+        <v>361</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -12930,7 +13004,7 @@
       </c>
       <c r="L113" s="2"/>
       <c r="M113" t="s" s="2">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -12939,7 +13013,7 @@
       </c>
       <c r="Q113" s="2"/>
       <c r="R113" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="S113" t="s" s="2">
         <v>74</v>
@@ -12981,7 +13055,7 @@
         <v>74</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>80</v>
@@ -13001,10 +13075,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>348</v>
+        <v>362</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13038,7 +13112,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>74</v>
@@ -13080,7 +13154,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13100,10 +13174,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13126,10 +13200,10 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>350</v>
+        <v>364</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="M115" s="2"/>
       <c r="N115" s="2"/>
@@ -13181,7 +13255,7 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>75</v>
@@ -13201,13 +13275,13 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>353</v>
+        <v>367</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>74</v>
@@ -13229,12 +13303,16 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="L116" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="M116" s="2"/>
       <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
+      <c r="O116" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="P116" t="s" s="2">
         <v>74</v>
       </c>
@@ -13282,7 +13360,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -13302,10 +13380,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>354</v>
+        <v>368</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -13403,10 +13481,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>355</v>
+        <v>369</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13504,10 +13582,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13605,10 +13683,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -13706,10 +13784,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -13809,10 +13887,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -13912,10 +13990,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14015,10 +14093,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14118,10 +14196,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14219,10 +14297,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14249,7 +14327,7 @@
       </c>
       <c r="L126" s="2"/>
       <c r="M126" t="s" s="2">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -14258,7 +14336,7 @@
       </c>
       <c r="Q126" s="2"/>
       <c r="R126" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="S126" t="s" s="2">
         <v>74</v>
@@ -14300,7 +14378,7 @@
         <v>74</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>80</v>
@@ -14320,10 +14398,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>364</v>
+        <v>378</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -14357,7 +14435,7 @@
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>74</v>
@@ -14399,7 +14477,7 @@
         <v>74</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -14419,10 +14497,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -14445,10 +14523,10 @@
         <v>74</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="M128" s="2"/>
       <c r="N128" s="2"/>
@@ -14500,7 +14578,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>75</v>
@@ -14520,13 +14598,13 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>369</v>
+        <v>383</v>
       </c>
       <c r="D129" t="s" s="2">
         <v>74</v>
@@ -14548,12 +14626,16 @@
         <v>74</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="L129" s="2"/>
+        <v>333</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>334</v>
+      </c>
       <c r="M129" s="2"/>
       <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
+      <c r="O129" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="P129" t="s" s="2">
         <v>74</v>
       </c>
@@ -14601,7 +14683,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -14621,10 +14703,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>370</v>
+        <v>384</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -14722,10 +14804,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -14823,10 +14905,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>372</v>
+        <v>386</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>324</v>
+        <v>338</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -14924,10 +15006,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15025,10 +15107,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>374</v>
+        <v>388</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>326</v>
+        <v>340</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15128,10 +15210,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>375</v>
+        <v>389</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>327</v>
+        <v>341</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15231,10 +15313,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15334,10 +15416,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>377</v>
+        <v>391</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>329</v>
+        <v>343</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -15437,10 +15519,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>378</v>
+        <v>392</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>330</v>
+        <v>344</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -15538,10 +15620,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>379</v>
+        <v>393</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -15568,7 +15650,7 @@
       </c>
       <c r="L139" s="2"/>
       <c r="M139" t="s" s="2">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -15577,7 +15659,7 @@
       </c>
       <c r="Q139" s="2"/>
       <c r="R139" t="s" s="2">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="S139" t="s" s="2">
         <v>74</v>
@@ -15619,7 +15701,7 @@
         <v>74</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>331</v>
+        <v>345</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
@@ -15639,10 +15721,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>380</v>
+        <v>394</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -15676,7 +15758,7 @@
       </c>
       <c r="Q140" s="2"/>
       <c r="R140" t="s" s="2">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="S140" t="s" s="2">
         <v>74</v>
@@ -15718,7 +15800,7 @@
         <v>74</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>80</v>
@@ -15738,10 +15820,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -15764,10 +15846,10 @@
         <v>74</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="M141" s="2"/>
       <c r="N141" s="2"/>
@@ -15819,7 +15901,7 @@
         <v>74</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>75</v>
